--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33819510</v>
+        <v>80208472</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80208472</v>
+        <v>80213057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1030592271</v>
+        <v>80830605</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1014192228</v>
+        <v>1030578335</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1019131043</v>
+        <v>1024512643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1014248976</v>
+        <v>1013614915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1018432981</v>
+        <v>93298014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1010044018</v>
+        <v>1014232367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1030635367</v>
+        <v>1078180826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1073687003</v>
+        <v>1031142560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1031142560</v>
+        <v>1097332216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80213057</v>
+        <v>33819510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11204332</v>
+        <v>35379078</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1022971025</v>
+        <v>1012466465</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1013614915</v>
+        <v>1018434197</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80912134</v>
+        <v>1018432981</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1012466465</v>
+        <v>1016039845</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1012406573</v>
+        <v>93138251</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1014232367</v>
+        <v>1016066574</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93298014</v>
+        <v>1014248976</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1032416590</v>
+        <v>1073721158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1129568417</v>
+        <v>1073687003</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1054681147</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>79822166</v>
+        <v>80251217</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80251217</v>
+        <v>11204332</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1024593756</v>
+        <v>80912134</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1014238905</v>
+        <v>1014192228</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1018434197</v>
+        <v>1013630135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1016039845</v>
+        <v>1012406573</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1000272392</v>
+        <v>1024593756</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>94446125</v>
+        <v>1000272392</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1030578335</v>
+        <v>1022971025</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1097332216</v>
+        <v>1032416590</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1078180826</v>
+        <v>1072719991</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1073721158</v>
+        <v>1127621316</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39724105</v>
+        <v>79822166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35379078</v>
+        <v>39724105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1022370155</v>
+        <v>1019131043</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1013630135</v>
+        <v>1030592271</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1020792634</v>
+        <v>1010044018</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>80830605</v>
+        <v>1020792634</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1016066574</v>
+        <v>1022370155</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>93138251</v>
+        <v>94446125</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1024512643</v>
+        <v>1014238905</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1073234269</v>
+        <v>1129568417</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1127621316</v>
+        <v>1073234269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1072719991</v>
+        <v>1054681147</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Empresa</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,6 +470,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,6 +498,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,6 +526,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -534,6 +554,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -557,6 +582,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -580,6 +610,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -603,6 +638,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -626,6 +666,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -649,6 +694,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -672,6 +722,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -695,6 +750,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -718,6 +778,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -741,6 +806,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -764,6 +834,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -787,6 +862,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -810,6 +890,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -833,6 +918,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -856,6 +946,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -879,6 +974,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -902,6 +1002,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -925,6 +1030,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -948,6 +1058,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -971,6 +1086,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -994,6 +1114,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1017,6 +1142,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1040,6 +1170,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1063,6 +1198,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1086,6 +1226,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1109,6 +1254,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1132,6 +1282,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1155,6 +1310,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1178,6 +1338,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1201,6 +1366,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1224,6 +1394,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1247,6 +1422,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1270,6 +1450,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1293,6 +1478,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1316,6 +1506,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1339,6 +1534,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1362,6 +1562,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1385,6 +1590,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1408,6 +1618,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1431,6 +1646,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1454,6 +1674,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1477,6 +1702,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1500,6 +1730,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1523,6 +1758,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1546,6 +1786,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1567,6 +1812,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grupo A</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1588,6 +1838,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Grupo B</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1609,6 +1864,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Grupo C</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1630,6 +1890,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grupo D</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1651,6 +1916,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grupo E</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1672,6 +1942,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grupo A</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1693,6 +1968,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grupo B</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1714,6 +1994,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Grupo C</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1735,6 +2020,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Grupo D</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1756,6 +2046,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Grupo E</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1777,6 +2072,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Grupo A</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1798,6 +2098,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Grupo B</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1819,6 +2124,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grupo C</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1840,6 +2150,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grupo D</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1861,6 +2176,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grupo E</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1882,6 +2202,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grupo A</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1903,6 +2228,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grupo B</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1924,6 +2254,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grupo C</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1945,6 +2280,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Grupo D</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1966,6 +2306,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Grupo E</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1987,6 +2332,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Grupo A</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2008,6 +2358,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Grupo B</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2029,6 +2384,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grupo C</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2050,6 +2410,11 @@
           <t>Cablemovil</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grupo D</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2069,6 +2434,11 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grupo E</t>
         </is>
       </c>
     </row>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,656 +1792,6 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AA01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AA02</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AA03</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AA04</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AA05</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AA06</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AA07</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AA08</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AA09</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AA10</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AA11</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>AA12</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>AA13</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>AA14</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>AA15</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>AA16</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>AA17</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>AA18</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>AA19</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>AA20</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AA21</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>AA22</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>AA23</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>AA24</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>AA25</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>Grupo</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>GrupoAsignado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +480,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +513,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,6 +546,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -559,6 +579,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -587,6 +612,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -615,6 +645,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -643,6 +678,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -671,6 +711,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -699,6 +744,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -727,6 +777,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,6 +810,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -783,6 +843,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,6 +876,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -839,6 +909,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,6 +942,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -895,6 +975,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -923,6 +1008,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -951,6 +1041,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -979,6 +1074,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1007,6 +1107,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1035,6 +1140,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1063,6 +1173,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1091,6 +1206,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1119,6 +1239,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1147,6 +1272,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1175,6 +1305,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1203,6 +1338,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1231,6 +1371,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1259,6 +1404,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1287,6 +1437,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1315,6 +1470,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1343,6 +1503,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1371,6 +1536,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1399,6 +1569,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1427,6 +1602,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1455,6 +1635,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1483,6 +1668,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1511,6 +1701,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1539,6 +1734,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1567,6 +1767,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1595,6 +1800,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1623,6 +1833,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1651,6 +1866,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1679,6 +1899,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1707,6 +1932,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1735,6 +1965,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1763,6 +1998,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1791,6 +2031,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1817,6 +2062,7 @@
           <t>Grupo B</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1843,6 +2089,7 @@
           <t>Grupo E</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1869,6 +2116,7 @@
           <t>Grupo E</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1895,6 +2143,7 @@
           <t>Grupo D</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1921,6 +2170,7 @@
           <t>Grupo A</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1947,6 +2197,7 @@
           <t>Grupo A</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1973,6 +2224,7 @@
           <t>Grupo D</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1999,6 +2251,7 @@
           <t>Grupo B</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2025,6 +2278,7 @@
           <t>Grupo C</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2051,6 +2305,7 @@
           <t>Grupo A</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2077,6 +2332,7 @@
           <t>Grupo E</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2103,6 +2359,7 @@
           <t>Grupo D</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2129,6 +2386,7 @@
           <t>Grupo D</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2155,6 +2413,7 @@
           <t>Grupo C</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2181,6 +2440,7 @@
           <t>Grupo A</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2207,6 +2467,7 @@
           <t>Grupo E</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2233,6 +2494,7 @@
           <t>Grupo D</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2259,6 +2521,7 @@
           <t>Grupo B</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2285,6 +2548,7 @@
           <t>Grupo A</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2311,6 +2575,7 @@
           <t>Grupo C</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2337,6 +2602,7 @@
           <t>Grupo C</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2363,6 +2629,7 @@
           <t>Grupo C</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2389,6 +2656,7 @@
           <t>Grupo B</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2415,6 +2683,7 @@
           <t>Grupo E</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2441,6 +2710,7 @@
           <t>Grupo B</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793A058F-1EC0-4346-9160-40AD7F37F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9735E192-09E1-4D0A-BA7F-514DC43B90A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="85">
   <si>
     <t>Cargo</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>Tecnico B</t>
+  </si>
+  <si>
+    <t>AA26</t>
+  </si>
+  <si>
+    <t>AA27</t>
   </si>
 </sst>
 </file>
@@ -668,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" style="1" customWidth="1"/>
@@ -1861,6 +1867,34 @@
         <v>3</v>
       </c>
     </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9735E192-09E1-4D0A-BA7F-514DC43B90A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04394AEC-A8C3-4390-9E75-E4CC897EFA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="90">
   <si>
     <t>Cargo</t>
   </si>
@@ -289,6 +289,21 @@
   </si>
   <si>
     <t>AA27</t>
+  </si>
+  <si>
+    <t>Supervisor 1</t>
+  </si>
+  <si>
+    <t>Supervisor 2</t>
+  </si>
+  <si>
+    <t>Supervisor 3</t>
+  </si>
+  <si>
+    <t>Supervisor 4</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
   </si>
 </sst>
 </file>
@@ -674,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" style="1" customWidth="1"/>
@@ -703,16 +718,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1">
-        <v>11204332</v>
+        <v>1111111</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D2" s="1">
+        <v>5000000</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -720,16 +735,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1">
-        <v>33819510</v>
+        <v>2222222</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D3" s="1">
+        <v>5000000</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -737,16 +752,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1">
-        <v>35379078</v>
+        <v>3333333</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5000000</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -754,16 +769,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1">
-        <v>39724105</v>
+        <v>444444</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5000000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -771,10 +786,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1">
-        <v>79822166</v>
+        <v>11204332</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>80</v>
@@ -788,10 +803,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1">
-        <v>80208472</v>
+        <v>33819510</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>80</v>
@@ -805,10 +820,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
-        <v>80213057</v>
+        <v>35379078</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>80</v>
@@ -822,10 +837,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1">
-        <v>80251217</v>
+        <v>39724105</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>80</v>
@@ -839,16 +854,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1">
-        <v>80830605</v>
+        <v>79822166</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4028000</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -856,16 +871,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
-        <v>80912134</v>
+        <v>80208472</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4028000</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
@@ -873,16 +888,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>93138251</v>
+        <v>80213057</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4028000</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>3</v>
@@ -890,16 +905,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1">
-        <v>93298014</v>
+        <v>80251217</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4028000</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
@@ -907,10 +922,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B14" s="1">
-        <v>94446125</v>
+        <v>80830605</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>81</v>
@@ -924,10 +939,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B15" s="1">
-        <v>1000272392</v>
+        <v>80912134</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>81</v>
@@ -941,10 +956,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B16" s="1">
-        <v>1010044018</v>
+        <v>93138251</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>81</v>
@@ -958,10 +973,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1">
-        <v>1012406573</v>
+        <v>93298014</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>81</v>
@@ -975,10 +990,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1">
-        <v>1012466465</v>
+        <v>94446125</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>81</v>
@@ -992,10 +1007,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B19" s="1">
-        <v>1013614915</v>
+        <v>1000272392</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>81</v>
@@ -1009,10 +1024,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="1">
-        <v>1013630135</v>
+        <v>1010044018</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>81</v>
@@ -1026,10 +1041,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1">
-        <v>1014192228</v>
+        <v>1012406573</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>81</v>
@@ -1043,10 +1058,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1">
-        <v>1014232367</v>
+        <v>1012466465</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>81</v>
@@ -1060,10 +1075,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1">
-        <v>1014238905</v>
+        <v>1013614915</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>81</v>
@@ -1077,10 +1092,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1">
-        <v>1014248976</v>
+        <v>1013630135</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>81</v>
@@ -1094,10 +1109,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1">
-        <v>1016039845</v>
+        <v>1014192228</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>81</v>
@@ -1111,10 +1126,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1">
-        <v>1016066574</v>
+        <v>1014232367</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>81</v>
@@ -1128,10 +1143,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1">
-        <v>1018432981</v>
+        <v>1014238905</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>81</v>
@@ -1145,10 +1160,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1">
-        <v>1018434197</v>
+        <v>1014248976</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>81</v>
@@ -1162,10 +1177,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1">
-        <v>1019131043</v>
+        <v>1016039845</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>81</v>
@@ -1179,10 +1194,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1">
-        <v>1020792634</v>
+        <v>1016066574</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>81</v>
@@ -1196,10 +1211,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1">
-        <v>1022370155</v>
+        <v>1018432981</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>81</v>
@@ -1213,10 +1228,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1">
-        <v>1022971025</v>
+        <v>1018434197</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>81</v>
@@ -1230,10 +1245,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
-        <v>1024512643</v>
+        <v>1019131043</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>81</v>
@@ -1247,10 +1262,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B34" s="1">
-        <v>1024534468</v>
+        <v>1020792634</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>81</v>
@@ -1264,10 +1279,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35" s="1">
-        <v>1024593756</v>
+        <v>1022370155</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>81</v>
@@ -1281,10 +1296,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1">
-        <v>1030578335</v>
+        <v>1022971025</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>81</v>
@@ -1298,10 +1313,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1">
-        <v>1030592271</v>
+        <v>1024512643</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>81</v>
@@ -1315,16 +1330,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1">
-        <v>1030635367</v>
+        <v>1024534468</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2968000</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>3</v>
@@ -1332,16 +1347,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B39" s="1">
-        <v>1031142560</v>
+        <v>1024593756</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2968000</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>3</v>
@@ -1349,16 +1364,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1">
-        <v>1032416590</v>
+        <v>1030578335</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2968000</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>3</v>
@@ -1366,16 +1381,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1">
-        <v>1054681147</v>
+        <v>1030592271</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2968000</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>3</v>
@@ -1383,10 +1398,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1">
-        <v>1072719991</v>
+        <v>1030635367</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>82</v>
@@ -1400,10 +1415,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1073234269</v>
+        <v>1031142560</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>82</v>
@@ -1417,10 +1432,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1073687003</v>
+        <v>1032416590</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>82</v>
@@ -1434,10 +1449,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B45" s="1">
-        <v>1073721158</v>
+        <v>1054681147</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>82</v>
@@ -1451,10 +1466,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B46" s="1">
-        <v>1078180826</v>
+        <v>1072719991</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>82</v>
@@ -1468,10 +1483,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1">
-        <v>1097332216</v>
+        <v>1073234269</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>82</v>
@@ -1485,10 +1500,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="B48" s="1">
-        <v>1127621316</v>
+        <v>1073687003</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>82</v>
@@ -1502,10 +1517,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="B49" s="1">
-        <v>1129568417</v>
+        <v>1073721158</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>82</v>
@@ -1519,13 +1534,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1078180826</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2544000</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>3</v>
@@ -1533,13 +1551,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>7</v>
+        <v>55</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1097332216</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2544000</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>3</v>
@@ -1547,13 +1568,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1127621316</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2544000</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>3</v>
@@ -1561,13 +1585,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1129568417</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2544000</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>3</v>
@@ -1575,7 +1602,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
@@ -1589,7 +1616,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>5</v>
@@ -1603,7 +1630,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>5</v>
@@ -1617,7 +1644,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>5</v>
@@ -1631,7 +1658,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>5</v>
@@ -1645,7 +1672,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>5</v>
@@ -1659,7 +1686,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>5</v>
@@ -1673,7 +1700,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>5</v>
@@ -1687,7 +1714,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>5</v>
@@ -1701,7 +1728,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -1715,7 +1742,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>5</v>
@@ -1729,7 +1756,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>5</v>
@@ -1743,7 +1770,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>5</v>
@@ -1757,7 +1784,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>5</v>
@@ -1771,7 +1798,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>5</v>
@@ -1785,7 +1812,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
@@ -1799,7 +1826,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>5</v>
@@ -1813,7 +1840,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>5</v>
@@ -1827,7 +1854,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>5</v>
@@ -1841,7 +1868,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>5</v>
@@ -1855,7 +1882,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>5</v>
@@ -1869,7 +1896,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>5</v>
@@ -1883,15 +1910,71 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="3">
-        <v>1751000</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>3</v>
       </c>
     </row>
